--- a/design_issues/sonarqube/Merged_Issues.xlsx
+++ b/design_issues/sonarqube/Merged_Issues.xlsx
@@ -489,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="84.1796875" customWidth="1"/>
@@ -780,16 +780,6 @@
         <v>38</v>
       </c>
       <c r="C29" s="4"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>30</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
